--- a/gte/nodes/P/compressor_stage_1_blade_rotor_coordinates_foil.xlsx
+++ b/gte/nodes/P/compressor_stage_1_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.0035127614558252405</v>
       </c>
       <c r="B2">
-        <v>0.00718656480585925</v>
+        <v>0.0064395056815530474</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.007025522911650481</v>
       </c>
       <c r="B3">
-        <v>0.011531396999870458</v>
+        <v>0.010132492630266372</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.010538284367475722</v>
       </c>
       <c r="B4">
-        <v>0.015284878177502344</v>
+        <v>0.013313897174392684</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.014051045823300962</v>
       </c>
       <c r="B5">
-        <v>0.01859057102625403</v>
+        <v>0.016115332025286873</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.017563807279126202</v>
       </c>
       <c r="B6">
-        <v>0.021515280013988353</v>
+        <v>0.018594109632030391</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.021076568734951444</v>
       </c>
       <c r="B7">
-        <v>0.024100805745746676</v>
+        <v>0.020784804379817792</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.024589330190776686</v>
       </c>
       <c r="B8">
-        <v>0.026375740545875718</v>
+        <v>0.022709659660069839</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.028102091646601924</v>
       </c>
       <c r="B9">
-        <v>0.028375708952939636</v>
+        <v>0.024399533597886758</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.031614853102427162</v>
       </c>
       <c r="B10">
-        <v>0.030137427394701623</v>
+        <v>0.02588699810069511</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.035127614558252404</v>
       </c>
       <c r="B11">
-        <v>0.031694947641503622</v>
+        <v>0.027202865471547377</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.038640376014077646</v>
       </c>
       <c r="B12">
-        <v>0.033068838370245886</v>
+        <v>0.028364847821892226</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.042153137469902888</v>
       </c>
       <c r="B13">
-        <v>0.034228400541483212</v>
+        <v>0.029340016101137095</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.045665898925728129</v>
       </c>
       <c r="B14">
-        <v>0.035156668917022356</v>
+        <v>0.030109445667760065</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.049178660381553371</v>
       </c>
       <c r="B15">
-        <v>0.035942881180023478</v>
+        <v>0.030760870678562893</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.052691421837378606</v>
       </c>
       <c r="B16">
-        <v>0.036668794888120852</v>
+        <v>0.031374726091393759</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.056204183293203848</v>
       </c>
       <c r="B17">
-        <v>0.037280044175491946</v>
+        <v>0.031895591269962692</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.05971694474902909</v>
       </c>
       <c r="B18">
-        <v>0.037705344784873418</v>
+        <v>0.032251299567613863</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.063229706204854325</v>
       </c>
       <c r="B19">
-        <v>0.037941862316695357</v>
+        <v>0.032438555890365976</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.066742467660679566</v>
       </c>
       <c r="B20">
-        <v>0.038003874835811267</v>
+        <v>0.03247128303240638</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.070255229116504808</v>
       </c>
       <c r="B21">
-        <v>0.037905660407074618</v>
+        <v>0.032363403787922441</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.07376799057233005</v>
       </c>
       <c r="B22">
-        <v>0.0376588325999282</v>
+        <v>0.032126291499076004</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.077280752028155292</v>
       </c>
       <c r="B23">
-        <v>0.037264347002172016</v>
+        <v>0.031761121699926939</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.080793513483980534</v>
       </c>
       <c r="B24">
-        <v>0.036720494706195393</v>
+        <v>0.0312665204725096</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.084306274939805775</v>
       </c>
       <c r="B25">
-        <v>0.036025566804387642</v>
+        <v>0.030641113898858378</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.087819036395631017</v>
       </c>
       <c r="B26">
-        <v>0.03517716026612798</v>
+        <v>0.0298829680124301</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.091331797851456259</v>
       </c>
       <c r="B27">
-        <v>0.034170095568755318</v>
+        <v>0.028987908652371493</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.0948445593072815</v>
       </c>
       <c r="B28">
-        <v>0.032998499066598456</v>
+        <v>0.027951201609251752</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.098357320763106743</v>
       </c>
       <c r="B29">
-        <v>0.031656497113986208</v>
+        <v>0.026768112673640081</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.10187008221893198</v>
       </c>
       <c r="B30">
-        <v>0.030139573293426168</v>
+        <v>0.025435476312922714</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.10538284367475721</v>
       </c>
       <c r="B31">
-        <v>0.028448640100141077</v>
+        <v>0.023956401701754088</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.10889560513058245</v>
       </c>
       <c r="B32">
-        <v>0.026585967257532438</v>
+        <v>0.022335566691605652</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.1124083665864077</v>
       </c>
       <c r="B33">
-        <v>0.024553824489001775</v>
+        <v>0.020577649133948883</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.11592112804223294</v>
       </c>
       <c r="B34">
-        <v>0.02235074990394215</v>
+        <v>0.018684095253200764</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.11943388949805818</v>
       </c>
       <c r="B35">
-        <v>0.01996035515571281</v>
+        <v>0.016643424765560359</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.12294665095388341</v>
       </c>
       <c r="B36">
-        <v>0.01736252028366456</v>
+        <v>0.014440925760172254</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.12645941240970865</v>
       </c>
       <c r="B37">
-        <v>0.014537125327148166</v>
+        <v>0.01206188632618101</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.12997217386553389</v>
       </c>
       <c r="B38">
-        <v>0.011455338677961039</v>
+        <v>0.0094839994576206531</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.13348493532135913</v>
       </c>
       <c r="B39">
-        <v>0.0080534821376870049</v>
+        <v>0.0066545777680829185</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.13699769677718438</v>
       </c>
       <c r="B40">
-        <v>0.0042591658603565053</v>
+        <v>0.0035133387760489729</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -677,7 +677,7 @@
         <v>0.14051045823300962</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>-2.4374679051706041E-19</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.13699769677718438</v>
       </c>
       <c r="B43">
-        <v>0.0017924331057460462</v>
+        <v>0.0010466060214385136</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.13348493532135913</v>
       </c>
       <c r="B44">
-        <v>0.0035436584702403357</v>
+        <v>0.0021447541006362511</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.12997217386553389</v>
       </c>
       <c r="B45">
-        <v>0.0052216638587835569</v>
+        <v>0.0032503246384431739</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.12645941240970865</v>
       </c>
       <c r="B46">
-        <v>0.0067944370366764054</v>
+        <v>0.00431919803570925</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.12294665095388341</v>
       </c>
       <c r="B47">
-        <v>0.0082353768278194718</v>
+        <v>0.005313782304327162</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.11943388949805818</v>
       </c>
       <c r="B48">
-        <v>0.009539526290512924</v>
+        <v>0.0062225959003604694</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.11592112804223294</v>
       </c>
       <c r="B49">
-        <v>0.010707339541656846</v>
+        <v>0.0070406848909154579</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.1124083665864077</v>
       </c>
       <c r="B50">
-        <v>0.011739270698151297</v>
+        <v>0.0077630953430984041</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.10889560513058245</v>
       </c>
       <c r="B51">
-        <v>0.012637798976372834</v>
+        <v>0.0083873984104460477</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.10538284367475721</v>
       </c>
       <c r="B52">
-        <v>0.013413503990603967</v>
+        <v>0.008921265592216978</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.10187008221893198</v>
       </c>
       <c r="B53">
-        <v>0.014078990454603689</v>
+        <v>0.0093748934741002335</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.098357320763106743</v>
       </c>
       <c r="B54">
-        <v>0.014646863082131001</v>
+        <v>0.009758478641784871</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.0948445593072815</v>
       </c>
       <c r="B55">
-        <v>0.015127516254548312</v>
+        <v>0.01008021879720161</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.091331797851456259</v>
       </c>
       <c r="B56">
-        <v>0.015522503023631706</v>
+        <v>0.010340316107247883</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.087819036395631017</v>
       </c>
       <c r="B57">
-        <v>0.015831166108760675</v>
+        <v>0.010536973855062798</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.084306274939805775</v>
       </c>
       <c r="B58">
-        <v>0.016052848229314718</v>
+        <v>0.010668395323785464</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.080793513483980534</v>
       </c>
       <c r="B59">
-        <v>0.016186983435276962</v>
+        <v>0.010733009201591174</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.077280752028155292</v>
       </c>
       <c r="B60">
-        <v>0.01623337109904505</v>
+        <v>0.01073014579679997</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.07376799057233005</v>
       </c>
       <c r="B61">
-        <v>0.016191901923620262</v>
+        <v>0.01065936082276807</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.070255229116504808</v>
       </c>
       <c r="B62">
-        <v>0.016062466612003872</v>
+        <v>0.010520209992851701</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.066742467660679566</v>
       </c>
       <c r="B63">
-        <v>0.0158470729421122</v>
+        <v>0.010314481138707319</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.063229706204854325</v>
       </c>
       <c r="B64">
-        <v>0.015556196991521717</v>
+        <v>0.010052890565192336</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.05971694474902909</v>
       </c>
       <c r="B65">
-        <v>0.015202431912723947</v>
+        <v>0.0097483866954643991</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.056204183293203848</v>
       </c>
       <c r="B66">
-        <v>0.014798370858210407</v>
+        <v>0.0094139179526811535</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.052691421837378606</v>
       </c>
       <c r="B67">
-        <v>0.014339011961622745</v>
+        <v>0.00904494316489565</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.049178660381553371</v>
       </c>
       <c r="B68">
-        <v>0.013748973281203149</v>
+        <v>0.00856696277974256</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.045665898925728129</v>
       </c>
       <c r="B69">
-        <v>0.012969029222368497</v>
+        <v>0.0079218059731061986</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.042153137469902888</v>
       </c>
       <c r="B70">
-        <v>0.01207495965463398</v>
+        <v>0.0071865752142878667</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.038640376014077646</v>
       </c>
       <c r="B71">
-        <v>0.011149286855820657</v>
+        <v>0.0064452963074669942</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.035127614558252404</v>
       </c>
       <c r="B72">
-        <v>0.010166497272874818</v>
+        <v>0.0056744151029185751</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.031614853102427162</v>
       </c>
       <c r="B73">
-        <v>0.0090863069603637457</v>
+        <v>0.004835877666357233</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.028102091646601924</v>
       </c>
       <c r="B74">
-        <v>0.0079173862342134353</v>
+        <v>0.0039412108791605591</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.024589330190776686</v>
       </c>
       <c r="B75">
-        <v>0.00668052703565339</v>
+        <v>0.0030144461498475112</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.021076568734951444</v>
       </c>
       <c r="B76">
-        <v>0.0053960535457684327</v>
+        <v>0.0020800521798395484</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.017563807279126202</v>
       </c>
       <c r="B77">
-        <v>0.004081160340776234</v>
+        <v>0.0011599899588182745</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.014051045823300962</v>
       </c>
       <c r="B78">
-        <v>0.0027409913375705448</v>
+        <v>0.00026575233660338954</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.010538284367475722</v>
       </c>
       <c r="B79">
-        <v>0.0013912040674223533</v>
+        <v>-0.00057977693568730753</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.007025522911650481</v>
       </c>
       <c r="B80">
-        <v>6.5743608056874543E-05</v>
+        <v>-0.0013331607615472132</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.0035127614558252405</v>
       </c>
       <c r="B81">
-        <v>-0.0011316543215349191</v>
+        <v>-0.0018787134458411224</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>0.00044694783742901345</v>
+        <v>-7.3512856284448965E-17</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.004138405902119815</v>
       </c>
       <c r="B2">
-        <v>0.0020466600635982717</v>
+        <v>0.002624122225313533</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.00827681180423963</v>
       </c>
       <c r="B3">
-        <v>0.0035368172082964515</v>
+        <v>0.0040643584623288043</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.012415217706359446</v>
       </c>
       <c r="B4">
-        <v>0.0049375351856780448</v>
+        <v>0.0053042124626382194</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.01655362360847926</v>
       </c>
       <c r="B5">
-        <v>0.0062689299098975448</v>
+        <v>0.0063985161307341205</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.020692029510599074</v>
       </c>
       <c r="B6">
-        <v>0.0075427950254035375</v>
+        <v>0.007369716953291929</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.024830435412718892</v>
       </c>
       <c r="B7">
-        <v>0.0087376350978209914</v>
+        <v>0.008230683672523869</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.028968841314838706</v>
       </c>
       <c r="B8">
-        <v>0.00983075966990922</v>
+        <v>0.0089890371215293717</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.03310724721695852</v>
       </c>
       <c r="B9">
-        <v>0.01082798727178857</v>
+        <v>0.0096565962670939857</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.037245653119078334</v>
       </c>
       <c r="B10">
-        <v>0.011740229269545526</v>
+        <v>0.010246104300330234</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.041384059021198148</v>
       </c>
       <c r="B11">
-        <v>0.012570259385770121</v>
+        <v>0.010769803175972386</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.045522464923317969</v>
       </c>
       <c r="B12">
-        <v>0.013318816932178259</v>
+        <v>0.011234271076734212</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.049660870825437783</v>
       </c>
       <c r="B13">
-        <v>0.013986641220485858</v>
+        <v>0.011623932333625655</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.0537992767275576</v>
       </c>
       <c r="B14">
-        <v>0.01457447484242917</v>
+        <v>0.011929499820121446</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.057937682629677412</v>
       </c>
       <c r="B15">
-        <v>0.015083073509825861</v>
+        <v>0.012188994431259197</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.062076088531797219</v>
       </c>
       <c r="B16">
-        <v>0.015513196214513934</v>
+        <v>0.012437288572081038</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.06621449443391704</v>
       </c>
       <c r="B17">
-        <v>0.015865601948331396</v>
+        <v>0.01264935266608427</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.070352900336036861</v>
       </c>
       <c r="B18">
-        <v>0.016140798864278029</v>
+        <v>0.012792842269336998</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.074491306238156668</v>
       </c>
       <c r="B19">
-        <v>0.016338291760000664</v>
+        <v>0.012866055449735393</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.078629712140276489</v>
       </c>
       <c r="B20">
-        <v>0.016457334594307933</v>
+        <v>0.012874950903132646</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.0827681180423963</v>
       </c>
       <c r="B21">
-        <v>0.016497181326008442</v>
+        <v>0.012825487325381949</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.086906523944516118</v>
       </c>
       <c r="B22">
-        <v>0.016457334594307933</v>
+        <v>0.012722559673706942</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.091044929846635939</v>
       </c>
       <c r="B23">
-        <v>0.016338291760000664</v>
+        <v>0.012566807950813077</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.095183335748755746</v>
       </c>
       <c r="B24">
-        <v>0.016140798864278025</v>
+        <v>0.012357808420776257</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.099321741650875567</v>
       </c>
       <c r="B25">
-        <v>0.015865601948331396</v>
+        <v>0.012095137347672383</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.10346014755299537</v>
       </c>
       <c r="B26">
-        <v>0.015513196214513933</v>
+        <v>0.011778190194062286</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.1075985534551152</v>
       </c>
       <c r="B27">
-        <v>0.015083073509825858</v>
+        <v>0.011405639216446491</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.111736959357235</v>
       </c>
       <c r="B28">
-        <v>0.014574474842429167</v>
+        <v>0.010975975869810457</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.11587536525935482</v>
       </c>
       <c r="B29">
-        <v>0.013986641220485853</v>
+        <v>0.010487691609139635</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.12001377116147464</v>
       </c>
       <c r="B30">
-        <v>0.013318816932178257</v>
+        <v>0.00994005839150091</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.12415217706359444</v>
       </c>
       <c r="B31">
-        <v>0.012570259385770123</v>
+        <v>0.0093354701822868924</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.12829058296571427</v>
       </c>
       <c r="B32">
-        <v>0.01174022926954553</v>
+        <v>0.00867710144897161</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.13242898886783408</v>
       </c>
       <c r="B33">
-        <v>0.01082798727178857</v>
+        <v>0.0079681266590291011</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.13656739476995389</v>
       </c>
       <c r="B34">
-        <v>0.0098307596699092163</v>
+        <v>0.0072104404181568618</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.14070580067207372</v>
       </c>
       <c r="B35">
-        <v>0.0087376350978209862</v>
+        <v>0.0064008178849462149</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.14484420657419353</v>
       </c>
       <c r="B36">
-        <v>0.0075427950254035375</v>
+        <v>0.0055347543562119473</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.14898261247631334</v>
       </c>
       <c r="B37">
-        <v>0.0062689299098975448</v>
+        <v>0.0046077451287688349</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.15312101837843314</v>
       </c>
       <c r="B38">
-        <v>0.0049375351856780422</v>
+        <v>0.0036121580436784817</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.15725942428055298</v>
       </c>
       <c r="B39">
-        <v>0.003536817208296445</v>
+        <v>0.0025278511189897545</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.16139783018267279</v>
       </c>
       <c r="B40">
-        <v>0.0020466600635982634</v>
+        <v>0.0013315549169983392</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.16553623608479259</v>
       </c>
       <c r="B41">
-        <v>0.00044694783742901367</v>
+        <v>-7.3225696689587841E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.16553623608479259</v>
       </c>
       <c r="B42">
-        <v>-0.00044694783742886638</v>
+        <v>-7.3584646183164247E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.16139783018267279</v>
       </c>
       <c r="B43">
-        <v>0.00024187592084216496</v>
+        <v>0.00024177752401913295</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.15725942428055298</v>
       </c>
       <c r="B44">
-        <v>0.000914723228713334</v>
+        <v>0.00053545698147319494</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.15312101837843314</v>
       </c>
       <c r="B45">
-        <v>0.0015527583271758992</v>
+        <v>0.0008581840347688111</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.14898261247631334</v>
       </c>
       <c r="B46">
-        <v>0.0021371454572211217</v>
+        <v>0.001187104346312681</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.14484420657419353</v>
       </c>
       <c r="B47">
-        <v>0.0026573308714261407</v>
+        <v>0.001502475390415012</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.14070580067207372</v>
       </c>
       <c r="B48">
-        <v>0.003135888868711606</v>
+        <v>0.0017970018890000423</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.13656739476995389</v>
       </c>
       <c r="B49">
-        <v>0.0035965297956238856</v>
+        <v>0.0020665003758955211</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.13242898886783408</v>
       </c>
       <c r="B50">
-        <v>0.0040343801428686828</v>
+        <v>0.0023067873849291942</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.12829058296571427</v>
       </c>
       <c r="B51">
-        <v>0.0044394123929482054</v>
+        <v>0.0025149428455043346</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.12415217706359444</v>
       </c>
       <c r="B52">
-        <v>0.0048095668513913293</v>
+        <v>0.0026931002693263151</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.12001377116147464</v>
       </c>
       <c r="B53">
-        <v>0.0051447757794835973</v>
+        <v>0.0028446565636760343</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.11587536525935482</v>
       </c>
       <c r="B54">
-        <v>0.005444971438510555</v>
+        <v>0.002973008635834393</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.111736959357235</v>
       </c>
       <c r="B55">
-        <v>0.0057100348310626017</v>
+        <v>0.0030807577832578583</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.1075985534551152</v>
       </c>
       <c r="B56">
-        <v>0.0059396419249495664</v>
+        <v>0.0031673228641051735</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.10346014755299537</v>
       </c>
       <c r="B57">
-        <v>0.0061334174292861348</v>
+        <v>0.0032313271267106506</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.099321741650875567</v>
       </c>
       <c r="B58">
-        <v>0.0062909860531869923</v>
+        <v>0.0032713938194086013</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.095183335748755746</v>
       </c>
       <c r="B59">
-        <v>0.0064121806500511067</v>
+        <v>0.0032863123944203922</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.091044929846635939</v>
       </c>
       <c r="B60">
-        <v>0.0064976666504145556</v>
+        <v>0.0032755371195156095</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.086906523944516118</v>
       </c>
       <c r="B61">
-        <v>0.0065483176290976955</v>
+        <v>0.0032386884663508923</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.0827681180423963</v>
       </c>
       <c r="B62">
-        <v>0.0065650071609208854</v>
+        <v>0.0031753869065828818</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.078629712140276489</v>
       </c>
       <c r="B63">
-        <v>0.0065483176290976955</v>
+        <v>0.0030863016222804993</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.074491306238156668</v>
       </c>
       <c r="B64">
-        <v>0.0064976666504145556</v>
+        <v>0.002976296637161791</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.070352900336036861</v>
       </c>
       <c r="B65">
-        <v>0.0064121806500511084</v>
+        <v>0.0028512846853570879</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.06621449443391704</v>
       </c>
       <c r="B66">
-        <v>0.006290986053186994</v>
+        <v>0.0027171785009967157</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.062076088531797219</v>
       </c>
       <c r="B67">
-        <v>0.0061334174292861348</v>
+        <v>0.0025722180337553143</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.057937682629677412</v>
       </c>
       <c r="B68">
-        <v>0.0059396419249495673</v>
+        <v>0.002383952095484762</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.0537992767275576</v>
       </c>
       <c r="B69">
-        <v>0.0057100348310626025</v>
+        <v>0.0021272267130696726</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.049660870825437783</v>
       </c>
       <c r="B70">
-        <v>0.0054449714385105576</v>
+        <v>0.0018367679113483781</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.045522464923317969</v>
       </c>
       <c r="B71">
-        <v>0.0051447757794835991</v>
+        <v>0.0015504365956714285</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.041384059021198148</v>
       </c>
       <c r="B72">
-        <v>0.0048095668513913285</v>
+        <v>0.0012587531954845431</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.037245653119078334</v>
       </c>
       <c r="B73">
-        <v>0.0044394123929482037</v>
+        <v>0.000945933820432896</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.03310724721695852</v>
       </c>
       <c r="B74">
-        <v>0.0040343801428686828</v>
+        <v>0.00061831777686430982</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.028968841314838706</v>
       </c>
       <c r="B75">
-        <v>0.0035965297956238873</v>
+        <v>0.00028789250291486485</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.024830435412718892</v>
       </c>
       <c r="B76">
-        <v>0.003135888868711609</v>
+        <v>-3.2885232828977277E-05</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.020692029510599074</v>
       </c>
       <c r="B77">
-        <v>0.0026573308714261407</v>
+        <v>-0.00033249945051178222</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.01655362360847926</v>
       </c>
       <c r="B78">
-        <v>0.0021371454572211217</v>
+        <v>-0.00060366665565260468</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.012415217706359446</v>
       </c>
       <c r="B79">
-        <v>0.0015527583271759005</v>
+        <v>-0.000833871171385891</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.00827681180423963</v>
       </c>
       <c r="B80">
-        <v>0.00091472322871333689</v>
+        <v>-0.0010010503618658479</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.004138405902119815</v>
       </c>
       <c r="B81">
-        <v>0.00024187592084216878</v>
+        <v>-0.0010507822157688623</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-0.00044694783742886643</v>
+        <v>-7.3512856284448965E-17</v>
       </c>
     </row>
   </sheetData>
@@ -1689,7 +1689,7 @@
         <v>0.0045665898925728128</v>
       </c>
       <c r="B2">
-        <v>0.0006375622565397681</v>
+        <v>0.00051334528818231331</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0091331797851456255</v>
       </c>
       <c r="B3">
-        <v>0.000995544077154872</v>
+        <v>0.00075348638627639492</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.013699769677718441</v>
       </c>
       <c r="B4">
-        <v>0.0013312876998966712</v>
+        <v>0.00097776461073818756</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.018266359570291251</v>
       </c>
       <c r="B5">
-        <v>0.0016555395086175937</v>
+        <v>0.0011969254238247021</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.022832949462864065</v>
       </c>
       <c r="B6">
-        <v>0.0019744652989246037</v>
+        <v>0.0014171337231115896</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.027399539355436882</v>
       </c>
       <c r="B7">
-        <v>0.00227590851344281</v>
+        <v>0.0016262321474490617</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.031966129248009692</v>
       </c>
       <c r="B8">
-        <v>0.0025470694952655437</v>
+        <v>0.0018114202714257376</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0365327191405825</v>
       </c>
       <c r="B9">
-        <v>0.0027908985423408823</v>
+        <v>0.0019756476713093077</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.041099309033155319</v>
       </c>
       <c r="B10">
-        <v>0.0030131726722142076</v>
+        <v>0.0021246906841540345</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.045665898925728129</v>
       </c>
       <c r="B11">
-        <v>0.003215225825965375</v>
+        <v>0.0022598826884813986</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.050232488818300947</v>
       </c>
       <c r="B12">
-        <v>0.0033972811755578606</v>
+        <v>0.0023814463231796863</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.054799078710873764</v>
       </c>
       <c r="B13">
-        <v>0.0035595618929551375</v>
+        <v>0.0024896042271371818</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.059365668603446567</v>
       </c>
       <c r="B14">
-        <v>0.0037023061591215252</v>
+        <v>0.0025845940845960025</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.063932258496019384</v>
       </c>
       <c r="B15">
-        <v>0.0038258121910247217</v>
+        <v>0.0026667137612135894</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.068498848388592187</v>
       </c>
       <c r="B16">
-        <v>0.003930393214633272</v>
+        <v>0.0027362761680012151</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.073065438281165</v>
       </c>
       <c r="B17">
-        <v>0.0040163624559157191</v>
+        <v>0.0027935942159701523</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.077632028173737822</v>
       </c>
       <c r="B18">
-        <v>0.0040839064879011552</v>
+        <v>0.0028388541980256202</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.082198618066310639</v>
       </c>
       <c r="B19">
-        <v>0.0041327052718608632</v>
+        <v>0.0028717359346486274</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.086765207958883456</v>
       </c>
       <c r="B20">
-        <v>0.0041623121161266773</v>
+        <v>0.0028917926282141307</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.091331797851456259</v>
       </c>
       <c r="B21">
-        <v>0.00417228032903043</v>
+        <v>0.0028985774810970861</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.095898387744029076</v>
       </c>
       <c r="B22">
-        <v>0.0041623121161266773</v>
+        <v>0.0028917926282141307</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.10046497763660189</v>
       </c>
       <c r="B23">
-        <v>0.0041327052718608632</v>
+        <v>0.0028717359346486274</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.10503156752917471</v>
       </c>
       <c r="B24">
-        <v>0.0040839064879011544</v>
+        <v>0.0028388541980256202</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.10959815742174753</v>
       </c>
       <c r="B25">
-        <v>0.0040163624559157183</v>
+        <v>0.0027935942159701519</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.11416474731432033</v>
       </c>
       <c r="B26">
-        <v>0.003930393214633272</v>
+        <v>0.0027362761680012151</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.11873133720689313</v>
       </c>
       <c r="B27">
-        <v>0.0038258121910247213</v>
+        <v>0.0026667137612135894</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.12329792709946595</v>
       </c>
       <c r="B28">
-        <v>0.0037023061591215239</v>
+        <v>0.002584594084596002</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.12786451699203877</v>
       </c>
       <c r="B29">
-        <v>0.0035595618929551366</v>
+        <v>0.0024896042271371813</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.1324311068846116</v>
       </c>
       <c r="B30">
-        <v>0.0033972811755578597</v>
+        <v>0.0023814463231796854</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.13699769677718438</v>
       </c>
       <c r="B31">
-        <v>0.0032152258259653759</v>
+        <v>0.002259882688481399</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.14156428666975721</v>
       </c>
       <c r="B32">
-        <v>0.0030131726722142081</v>
+        <v>0.0021246906841540349</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.14613087656233</v>
       </c>
       <c r="B33">
-        <v>0.0027908985423408823</v>
+        <v>0.0019756476713093077</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.15069746645490284</v>
       </c>
       <c r="B34">
-        <v>0.0025470694952655429</v>
+        <v>0.0018114202714257369</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.15526405634747564</v>
       </c>
       <c r="B35">
-        <v>0.0022759085134428083</v>
+        <v>0.0016262321474490606</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.15983064624004845</v>
       </c>
       <c r="B36">
-        <v>0.0019744652989246037</v>
+        <v>0.0014171337231115896</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.16439723613262128</v>
       </c>
       <c r="B37">
-        <v>0.0016555395086175937</v>
+        <v>0.0011969254238247021</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.16896382602519408</v>
       </c>
       <c r="B38">
-        <v>0.0013312876998966706</v>
+        <v>0.00097776461073818713</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.17353041591776691</v>
       </c>
       <c r="B39">
-        <v>0.00099554407715487028</v>
+        <v>0.00075348638627639394</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.17809700581033972</v>
       </c>
       <c r="B40">
-        <v>0.00063756225653976593</v>
+        <v>0.0005133452881823119</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.18266359570291252</v>
       </c>
       <c r="B42">
-        <v>-0.00024659585419893181</v>
+        <v>-0.00024659585419893192</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.17809700581033972</v>
       </c>
       <c r="B43">
-        <v>-0.00035819664429256128</v>
+        <v>-0.00048241361265001541</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.17353041591776691</v>
       </c>
       <c r="B44">
-        <v>-0.00045115160081219449</v>
+        <v>-0.000693209291690671</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.16896382602519408</v>
       </c>
       <c r="B45">
-        <v>-0.00053620526191415171</v>
+        <v>-0.00088972835107263516</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.16439723613262128</v>
       </c>
       <c r="B46">
-        <v>-0.00062410216575475386</v>
+        <v>-0.0010827162505476454</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.15983064624004845</v>
       </c>
       <c r="B47">
-        <v>-0.00072100630943698347</v>
+        <v>-0.0012783378852499975</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.15526405634747564</v>
       </c>
       <c r="B48">
-        <v>-0.00081475952585046947</v>
+        <v>-0.0014644358918442172</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.15069746645490284</v>
       </c>
       <c r="B49">
-        <v>-0.0008925606189898169</v>
+        <v>-0.0016282098428296225</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.14613087656233</v>
       </c>
       <c r="B50">
-        <v>-0.0009573584414828821</v>
+        <v>-0.0017726093125144565</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.14156428666975721</v>
       </c>
       <c r="B51">
-        <v>-0.0010149286480449643</v>
+        <v>-0.0019034106361051372</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.13699769677718438</v>
       </c>
       <c r="B52">
-        <v>-0.0010666040531078806</v>
+        <v>-0.0020219471905918575</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.1324311068846116</v>
       </c>
       <c r="B53">
-        <v>-0.001112606761032578</v>
+        <v>-0.0021284416134107528</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.12786451699203877</v>
       </c>
       <c r="B54">
-        <v>-0.0011531588761800043</v>
+        <v>-0.0022231165419979598</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.12329792709946595</v>
       </c>
       <c r="B55">
-        <v>-0.0011884975847173021</v>
+        <v>-0.0023062096592428244</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.11873133720689313</v>
       </c>
       <c r="B56">
-        <v>-0.0012189204000364012</v>
+        <v>-0.002378018829847534</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.11416474731432033</v>
       </c>
       <c r="B57">
-        <v>-0.0012447399173354282</v>
+        <v>-0.0024388569639674854</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.10959815742174753</v>
       </c>
       <c r="B58">
-        <v>-0.0012662687318125087</v>
+        <v>-0.0024890369717580759</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.10503156752917471</v>
       </c>
       <c r="B59">
-        <v>-0.001283692855487536</v>
+        <v>-0.0025287451453630708</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.10046497763660189</v>
       </c>
       <c r="B60">
-        <v>-0.0012966919676674676</v>
+        <v>-0.0025576613048797032</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.095898387744029076</v>
       </c>
       <c r="B61">
-        <v>-0.0013048191644810289</v>
+        <v>-0.0025753386523935753</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.091331797851456259</v>
       </c>
       <c r="B62">
-        <v>-0.0013076275420569436</v>
+        <v>-0.0025813303899902881</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.086765207958883456</v>
       </c>
       <c r="B63">
-        <v>-0.0013048191644810287</v>
+        <v>-0.0025753386523935753</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.082198618066310639</v>
       </c>
       <c r="B64">
-        <v>-0.0012966919676674676</v>
+        <v>-0.0025576613048797032</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.077632028173737822</v>
       </c>
       <c r="B65">
-        <v>-0.001283692855487536</v>
+        <v>-0.0025287451453630708</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.073065438281165</v>
       </c>
       <c r="B66">
-        <v>-0.0012662687318125089</v>
+        <v>-0.0024890369717580759</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.068498848388592187</v>
       </c>
       <c r="B67">
-        <v>-0.0012447399173354282</v>
+        <v>-0.0024388569639674854</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.063932258496019384</v>
       </c>
       <c r="B68">
-        <v>-0.0012189204000364014</v>
+        <v>-0.002378018829847534</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.059365668603446567</v>
       </c>
       <c r="B69">
-        <v>-0.0011884975847173021</v>
+        <v>-0.0023062096592428249</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.054799078710873764</v>
       </c>
       <c r="B70">
-        <v>-0.0011531588761800045</v>
+        <v>-0.00222311654199796</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.050232488818300947</v>
       </c>
       <c r="B71">
-        <v>-0.0011126067610325782</v>
+        <v>-0.0021284416134107532</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.045665898925728129</v>
       </c>
       <c r="B72">
-        <v>-0.0010666040531078806</v>
+        <v>-0.002021947190591857</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.041099309033155319</v>
       </c>
       <c r="B73">
-        <v>-0.0010149286480449641</v>
+        <v>-0.0019034106361051372</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0365327191405825</v>
       </c>
       <c r="B74">
-        <v>-0.0009573584414828821</v>
+        <v>-0.0017726093125144565</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.031966129248009692</v>
       </c>
       <c r="B75">
-        <v>-0.00089256061898981723</v>
+        <v>-0.0016282098428296232</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.027399539355436882</v>
       </c>
       <c r="B76">
-        <v>-0.00081475952585046991</v>
+        <v>-0.0014644358918442183</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.022832949462864065</v>
       </c>
       <c r="B77">
-        <v>-0.00072100630943698347</v>
+        <v>-0.0012783378852499975</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.018266359570291251</v>
       </c>
       <c r="B78">
-        <v>-0.00062410216575475386</v>
+        <v>-0.0010827162505476454</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.013699769677718441</v>
       </c>
       <c r="B79">
-        <v>-0.00053620526191415193</v>
+        <v>-0.00088972835107263548</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0091331797851456255</v>
       </c>
       <c r="B80">
-        <v>-0.00045115160081219487</v>
+        <v>-0.00069320929169067191</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0045665898925728128</v>
       </c>
       <c r="B81">
-        <v>-0.00035819664429256182</v>
+        <v>-0.00048241361265001666</v>
       </c>
     </row>
     <row r="82" spans="1:2">
